--- a/data/trans_camb/P1432-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1432-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; -0,28</t>
+          <t>-2,28; -0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,63</t>
+          <t>-1,72; 0,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,85</t>
+          <t>0,37; 3,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,24</t>
+          <t>-0,18; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,09</t>
+          <t>-0,55; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,0</t>
+          <t>-0,61; 1,03</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,84</t>
+          <t>-100,0; 9,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,58; 101,52</t>
+          <t>-83,85; 124,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 1034,34</t>
+          <t>-0,65; 857,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 940,86</t>
+          <t>-33,31; 626,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 156,16</t>
+          <t>-40,48; 176,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 147,55</t>
+          <t>-43,07; 155,16</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,57</t>
+          <t>-1,27; 0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,12</t>
+          <t>-1,51; 0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,93</t>
+          <t>-1,5; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,56</t>
+          <t>-1,8; 0,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,45</t>
+          <t>-1,07; 0,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,1</t>
+          <t>-1,41; 0,02</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,62; 118,54</t>
+          <t>-85,34; 97,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 34,06</t>
+          <t>-85,84; 42,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 82,94</t>
+          <t>-61,43; 79,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,66; 57,39</t>
+          <t>-73,01; 53,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 46,94</t>
+          <t>-58,16; 50,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,95; 14,47</t>
+          <t>-72,14; 8,36</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,8</t>
+          <t>-1,35; 0,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,29</t>
+          <t>-1,53; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,3</t>
+          <t>-1,44; 1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,48</t>
+          <t>-1,19; 1,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,67</t>
+          <t>-1,15; 0,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,59</t>
+          <t>-1,09; 0,55</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,1; 176,7</t>
+          <t>-80,17; 209,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 95,03</t>
+          <t>-91,91; 87,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 145,64</t>
+          <t>-63,91; 142,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 158,46</t>
+          <t>-56,5; 145,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,06; 76,57</t>
+          <t>-63,03; 69,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 66,91</t>
+          <t>-60,82; 62,62</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,76</t>
+          <t>-0,98; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,15</t>
+          <t>-1,46; -0,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,71</t>
+          <t>-1,42; 0,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,84</t>
+          <t>-1,49; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,49</t>
+          <t>-0,97; 0,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,25</t>
+          <t>-1,13; 0,2</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 134,82</t>
+          <t>-75,99; 157,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,11</t>
+          <t>-93,69; 3,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 63,93</t>
+          <t>-60,91; 66,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 91,11</t>
+          <t>-62,58; 85,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 51,77</t>
+          <t>-55,07; 40,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 28,33</t>
+          <t>-66,34; 21,62</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,02</t>
+          <t>-0,88; 0,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; -0,14</t>
+          <t>-1,03; -0,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,78</t>
+          <t>-0,48; 0,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,58</t>
+          <t>-0,67; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,2</t>
+          <t>-0,56; 0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,07</t>
+          <t>-0,63; 0,07</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 2,06</t>
+          <t>-65,09; 11,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,3; -17,1</t>
+          <t>-75,09; -19,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 66,75</t>
+          <t>-27,75; 62,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 50,63</t>
+          <t>-37,37; 44,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 18,4</t>
+          <t>-37,29; 18,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 8,09</t>
+          <t>-43,77; 6,21</t>
         </is>
       </c>
     </row>
